--- a/artfynd/A 29517-2026 artfynd.xlsx
+++ b/artfynd/A 29517-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888878</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888893</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888894</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888896</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888897</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888898</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,6 +1504,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888906</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888907</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1711,6 +1756,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888908</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1846,6 +1896,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888881</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1972,6 +2027,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888882</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2093,6 +2153,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888883</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2223,6 +2288,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888884</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2358,6 +2428,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888885</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2484,6 +2559,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888886</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2610,6 +2690,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888887</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2746,6 +2831,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888888</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2871,6 +2961,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888910</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3001,6 +3096,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888840</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3136,6 +3236,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888841</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3271,6 +3376,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888842</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3406,6 +3516,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888843</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3541,6 +3656,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888844</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3676,6 +3796,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888845</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3811,6 +3936,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888850</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3946,6 +4076,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888851</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4081,6 +4216,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888852</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4216,6 +4356,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888853</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4351,6 +4496,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888854</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4486,6 +4636,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888855</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4621,6 +4776,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888856</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4751,6 +4911,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888857</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4886,6 +5051,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888858</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5021,6 +5191,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888859</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5156,6 +5331,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888860</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5291,6 +5471,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888861</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5426,6 +5611,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888862</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5561,6 +5751,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888863</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5696,6 +5891,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888864</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5831,6 +6031,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888865</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5966,6 +6171,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888866</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6101,6 +6311,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888867</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6236,6 +6451,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888868</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6371,6 +6591,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888869</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6506,6 +6731,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888870</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6641,6 +6871,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888871</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6776,6 +7011,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888872</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6911,6 +7151,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888873</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7046,6 +7291,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888874</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7181,6 +7431,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888875</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7316,6 +7571,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888876</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7427,6 +7687,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888890</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7538,6 +7803,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888892</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7666,6 +7936,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888899</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7799,6 +8074,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888900</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7932,6 +8212,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888901</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8065,6 +8350,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888902</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8198,6 +8488,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888903</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8305,6 +8600,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888880</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8421,6 +8721,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888912</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8537,6 +8842,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888913</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8644,6 +8954,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888895</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8770,6 +9085,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888909</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8905,6 +9225,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888846</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9040,6 +9365,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888848</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9151,6 +9481,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888889</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9258,8 +9593,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132888879</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>